--- a/backend/Rwanda/upload-{model}.xlsx
+++ b/backend/Rwanda/upload-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1747358-A051-42A3-84BC-E0DC8B2F41A3}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA26B1-513C-4605-8266-51FD89385BA5}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carbon Credits" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="20">
   <si>
     <t>Units</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>CO2 emited - {model} scenario</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -579,13 +576,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2020</v>
       </c>
       <c r="D1" s="6">
         <v>2021</v>
@@ -918,16 +915,16 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
+      <c r="D1" s="6">
+        <v>2020</v>
       </c>
       <c r="E1" s="6">
         <v>2021</v>
@@ -1052,13 +1049,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" s="10">
         <v>0</v>
@@ -1186,13 +1183,13 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="10">
         <v>0</v>
@@ -1320,13 +1317,13 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="10">
         <v>0</v>
@@ -1454,147 +1451,147 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="10">
         <v>0</v>
@@ -1722,13 +1719,13 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="10">
         <v>0</v>
@@ -1856,13 +1853,13 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
@@ -1990,147 +1987,147 @@
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="19">
         <v>0</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -2258,13 +2255,13 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2392,147 +2389,147 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="10">
         <v>0</v>
@@ -2660,13 +2657,13 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="10">
         <v>0</v>
@@ -2794,13 +2791,13 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
@@ -2928,136 +2925,136 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="19">
         <v>0</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR16" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3075,13 +3072,13 @@
   <sheetData>
     <row r="1" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>3</v>
+      <c r="C1" s="6">
+        <v>2020</v>
       </c>
       <c r="D1" s="6">
         <v>2021</v>
@@ -3206,10 +3203,10 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -3337,10 +3334,10 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="10">
         <v>0</v>
@@ -3468,10 +3465,10 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="10">
         <v>0</v>
@@ -3599,141 +3596,141 @@
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="10">
         <v>0</v>
@@ -3861,10 +3858,10 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="10">
         <v>0</v>
@@ -3992,10 +3989,10 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
@@ -4123,133 +4120,133 @@
     </row>
     <row r="9" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Rwanda/upload-{model}.xlsx
+++ b/backend/Rwanda/upload-{model}.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA26B1-513C-4605-8266-51FD89385BA5}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A8EFD61-30C1-443F-B3FC-0D01029BE195}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carbon Credits" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="17">
   <si>
     <t>Units</t>
   </si>
@@ -70,19 +70,10 @@
     <t>OPEX</t>
   </si>
   <si>
-    <t>Tariff</t>
-  </si>
-  <si>
     <t>Demand</t>
   </si>
   <si>
-    <t>$/kWh</t>
-  </si>
-  <si>
     <t>kWh</t>
-  </si>
-  <si>
-    <t>Upstream Cost of Energy</t>
   </si>
   <si>
     <t>GRID</t>
@@ -300,6 +291,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -907,7 +902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9488325-B995-45A9-8828-C7E7D2622F95}">
-  <dimension ref="A1:AR16"/>
+  <dimension ref="A1:AR13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.6328125" customWidth="1"/>
@@ -915,7 +910,7 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>3</v>
@@ -1049,13 +1044,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2" s="10">
         <v>0</v>
@@ -1182,148 +1177,148 @@
       </c>
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>11</v>
+      <c r="A3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3" s="10">
-        <v>0</v>
-      </c>
-      <c r="P3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>0</v>
-      </c>
-      <c r="S3" s="10">
-        <v>0</v>
-      </c>
-      <c r="T3" s="10">
-        <v>0</v>
-      </c>
-      <c r="U3" s="10">
-        <v>0</v>
-      </c>
-      <c r="V3" s="10">
-        <v>0</v>
-      </c>
-      <c r="W3" s="10">
-        <v>0</v>
-      </c>
-      <c r="X3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="10">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR3" s="15" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D4" s="10">
         <v>0</v>
@@ -1450,145 +1445,145 @@
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>7</v>
+      <c r="A5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR5" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0</v>
+      </c>
+      <c r="T5" s="10">
+        <v>0</v>
+      </c>
+      <c r="U5" s="10">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10">
+        <v>0</v>
+      </c>
+      <c r="W5" s="10">
+        <v>0</v>
+      </c>
+      <c r="X5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>4</v>
@@ -1719,147 +1714,147 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
-        <v>0</v>
-      </c>
-      <c r="S7" s="10">
-        <v>0</v>
-      </c>
-      <c r="T7" s="10">
-        <v>0</v>
-      </c>
-      <c r="U7" s="10">
-        <v>0</v>
-      </c>
-      <c r="V7" s="10">
-        <v>0</v>
-      </c>
-      <c r="W7" s="10">
-        <v>0</v>
-      </c>
-      <c r="X7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="10">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR7" s="19" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>9</v>
+      <c r="A8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
@@ -1986,148 +1981,148 @@
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>8</v>
+      <c r="A9" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>7</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="N9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="U9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="V9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="W9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="X9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ9" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR9" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>10</v>
+      <c r="A10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D10" s="10">
         <v>0</v>
@@ -2254,14 +2249,14 @@
       </c>
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>11</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D11" s="10">
         <v>0</v>
@@ -2388,672 +2383,270 @@
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>7</v>
+      <c r="A12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ12" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR12" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>0</v>
+      </c>
+      <c r="S12" s="10">
+        <v>0</v>
+      </c>
+      <c r="T12" s="10">
+        <v>0</v>
+      </c>
+      <c r="U12" s="10">
+        <v>0</v>
+      </c>
+      <c r="V12" s="10">
+        <v>0</v>
+      </c>
+      <c r="W12" s="10">
+        <v>0</v>
+      </c>
+      <c r="X12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>8</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10">
-        <v>0</v>
-      </c>
-      <c r="J13" s="10">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10">
-        <v>0</v>
-      </c>
-      <c r="O13" s="10">
-        <v>0</v>
-      </c>
-      <c r="P13" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>0</v>
-      </c>
-      <c r="R13" s="10">
-        <v>0</v>
-      </c>
-      <c r="S13" s="10">
-        <v>0</v>
-      </c>
-      <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="10">
-        <v>0</v>
-      </c>
-      <c r="V13" s="10">
-        <v>0</v>
-      </c>
-      <c r="W13" s="10">
-        <v>0</v>
-      </c>
-      <c r="X13" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0</v>
-      </c>
-      <c r="E14" s="10">
-        <v>0</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10">
-        <v>0</v>
-      </c>
-      <c r="I14" s="10">
-        <v>0</v>
-      </c>
-      <c r="J14" s="10">
-        <v>0</v>
-      </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0</v>
-      </c>
-      <c r="M14" s="10">
-        <v>0</v>
-      </c>
-      <c r="N14" s="10">
-        <v>0</v>
-      </c>
-      <c r="O14" s="10">
-        <v>0</v>
-      </c>
-      <c r="P14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>0</v>
-      </c>
-      <c r="R14" s="10">
-        <v>0</v>
-      </c>
-      <c r="S14" s="10">
-        <v>0</v>
-      </c>
-      <c r="T14" s="10">
-        <v>0</v>
-      </c>
-      <c r="U14" s="10">
-        <v>0</v>
-      </c>
-      <c r="V14" s="10">
-        <v>0</v>
-      </c>
-      <c r="W14" s="10">
-        <v>0</v>
-      </c>
-      <c r="X14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="10">
-        <v>0</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0</v>
-      </c>
-      <c r="P15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0</v>
-      </c>
-      <c r="R15" s="10">
-        <v>0</v>
-      </c>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="10">
-        <v>0</v>
-      </c>
-      <c r="V15" s="10">
-        <v>0</v>
-      </c>
-      <c r="W15" s="10">
-        <v>0</v>
-      </c>
-      <c r="X15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="19">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR16" s="19" t="s">
+      <c r="D13" s="19">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="R13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="U13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="V13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="W13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="X13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR13" s="19" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3064,7 +2657,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BBA240-3A33-412F-B1CD-E7904F3C1D3D}">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -3206,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -3333,142 +2926,142 @@
       </c>
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>11</v>
+      <c r="A3" s="20" t="s">
+        <v>7</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10">
-        <v>0</v>
-      </c>
-      <c r="E3" s="10">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10">
-        <v>0</v>
-      </c>
-      <c r="M3" s="10">
-        <v>0</v>
-      </c>
-      <c r="N3" s="10">
-        <v>0</v>
-      </c>
-      <c r="O3" s="10">
-        <v>0</v>
-      </c>
-      <c r="P3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>0</v>
-      </c>
-      <c r="R3" s="10">
-        <v>0</v>
-      </c>
-      <c r="S3" s="10">
-        <v>0</v>
-      </c>
-      <c r="T3" s="10">
-        <v>0</v>
-      </c>
-      <c r="U3" s="10">
-        <v>0</v>
-      </c>
-      <c r="V3" s="10">
-        <v>0</v>
-      </c>
-      <c r="W3" s="10">
-        <v>0</v>
-      </c>
-      <c r="X3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="10">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="S3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="V3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ3" s="15" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>14</v>
+      <c r="A4" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C4" s="10">
         <v>0</v>
@@ -3595,139 +3188,139 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
-        <v>7</v>
+      <c r="A5" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ5" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10">
+        <v>0</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0</v>
+      </c>
+      <c r="T5" s="10">
+        <v>0</v>
+      </c>
+      <c r="U5" s="10">
+        <v>0</v>
+      </c>
+      <c r="V5" s="10">
+        <v>0</v>
+      </c>
+      <c r="W5" s="10">
+        <v>0</v>
+      </c>
+      <c r="X5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>18</v>
+      <c r="A6" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>4</v>
@@ -3857,395 +3450,133 @@
       </c>
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>19</v>
+      <c r="A7" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="10">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10">
-        <v>0</v>
-      </c>
-      <c r="P7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>0</v>
-      </c>
-      <c r="R7" s="10">
-        <v>0</v>
-      </c>
-      <c r="S7" s="10">
-        <v>0</v>
-      </c>
-      <c r="T7" s="10">
-        <v>0</v>
-      </c>
-      <c r="U7" s="10">
-        <v>0</v>
-      </c>
-      <c r="V7" s="10">
-        <v>0</v>
-      </c>
-      <c r="W7" s="10">
-        <v>0</v>
-      </c>
-      <c r="X7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="10">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>0</v>
-      </c>
-      <c r="S8" s="10">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10">
-        <v>0</v>
-      </c>
-      <c r="U8" s="10">
-        <v>0</v>
-      </c>
-      <c r="V8" s="10">
-        <v>0</v>
-      </c>
-      <c r="W8" s="10">
-        <v>0</v>
-      </c>
-      <c r="X8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ9" s="19" t="s">
+      <c r="C7" s="19">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="W7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ7" s="19" t="s">
         <v>6</v>
       </c>
     </row>

--- a/backend/Rwanda/upload-{model}.xlsx
+++ b/backend/Rwanda/upload-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305EC6AA-D4E6-4119-8B39-EFA622D8D338}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="13_ncr:1_{E7A8A98C-3045-4467-A4AE-AE11E8430C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE338B19-8150-4733-96F9-BCD979B8CBBA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="16">
   <si>
     <t>Units</t>
   </si>
@@ -62,9 +62,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Outputs</t>
-  </si>
-  <si>
     <t>D&amp;A</t>
   </si>
   <si>
@@ -83,13 +80,13 @@
     <t>OFF-GRID</t>
   </si>
   <si>
-    <t>Type - Inputs</t>
-  </si>
-  <si>
     <t>CAPEX - Growth</t>
   </si>
   <si>
     <t>CAPEX - Maintenance</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
 </sst>
 </file>
@@ -147,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,19 +165,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -248,16 +233,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -270,10 +249,16 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -557,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB732D8F-90AB-4000-AD46-068250289DC9}">
-  <dimension ref="A1:AR13"/>
+  <dimension ref="A1:AR11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.6328125" customWidth="1"/>
@@ -565,12 +550,12 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="6">
@@ -698,14 +683,14 @@
       </c>
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="10">
         <v>0</v>
@@ -833,146 +818,146 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10">
+        <v>0</v>
+      </c>
+      <c r="T3" s="10">
+        <v>0</v>
+      </c>
+      <c r="U3" s="10">
+        <v>0</v>
+      </c>
+      <c r="V3" s="10">
+        <v>0</v>
+      </c>
+      <c r="W3" s="10">
+        <v>0</v>
+      </c>
+      <c r="X3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="10">
@@ -1100,13 +1085,13 @@
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="A5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="10">
@@ -1234,282 +1219,282 @@
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
-        <v>0</v>
-      </c>
-      <c r="S6" s="10">
-        <v>0</v>
-      </c>
-      <c r="T6" s="10">
-        <v>0</v>
-      </c>
-      <c r="U6" s="10">
-        <v>0</v>
-      </c>
-      <c r="V6" s="10">
-        <v>0</v>
-      </c>
-      <c r="W6" s="10">
-        <v>0</v>
-      </c>
-      <c r="X6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="10">
-        <v>0</v>
+      <c r="A6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR6" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR7" s="19" t="s">
-        <v>6</v>
+      <c r="B7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>11</v>
+      <c r="C8" s="21" t="s">
+        <v>4</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
@@ -1636,145 +1621,145 @@
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR9" s="15" t="s">
-        <v>6</v>
+      <c r="A9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
+        <v>0</v>
+      </c>
+      <c r="S9" s="10">
+        <v>0</v>
+      </c>
+      <c r="T9" s="10">
+        <v>0</v>
+      </c>
+      <c r="U9" s="10">
+        <v>0</v>
+      </c>
+      <c r="V9" s="10">
+        <v>0</v>
+      </c>
+      <c r="W9" s="10">
+        <v>0</v>
+      </c>
+      <c r="X9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>15</v>
+      <c r="A10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>4</v>
@@ -1904,404 +1889,136 @@
       </c>
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>13</v>
+      <c r="A11" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0</v>
-      </c>
-      <c r="P11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0</v>
-      </c>
-      <c r="S11" s="10">
-        <v>0</v>
-      </c>
-      <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10">
-        <v>0</v>
-      </c>
-      <c r="V11" s="10">
-        <v>0</v>
-      </c>
-      <c r="W11" s="10">
-        <v>0</v>
-      </c>
-      <c r="X11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0</v>
-      </c>
-      <c r="J12" s="10">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10">
-        <v>0</v>
-      </c>
-      <c r="N12" s="10">
-        <v>0</v>
-      </c>
-      <c r="O12" s="10">
-        <v>0</v>
-      </c>
-      <c r="P12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>0</v>
-      </c>
-      <c r="R12" s="10">
-        <v>0</v>
-      </c>
-      <c r="S12" s="10">
-        <v>0</v>
-      </c>
-      <c r="T12" s="10">
-        <v>0</v>
-      </c>
-      <c r="U12" s="10">
-        <v>0</v>
-      </c>
-      <c r="V12" s="10">
-        <v>0</v>
-      </c>
-      <c r="W12" s="10">
-        <v>0</v>
-      </c>
-      <c r="X12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="19">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR13" s="19" t="s">
+      <c r="D11" s="17">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="W11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR11" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2325,7 +2042,7 @@
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6">
@@ -2654,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9488325-B995-45A9-8828-C7E7D2622F95}">
-  <dimension ref="A1:AR13"/>
+  <dimension ref="A1:AR11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.6328125" customWidth="1"/>
@@ -2662,12 +2379,12 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="6">
@@ -2795,14 +2512,14 @@
       </c>
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="10">
         <v>0</v>
@@ -2930,144 +2647,144 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR3" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10">
+        <v>0</v>
+      </c>
+      <c r="T3" s="10">
+        <v>0</v>
+      </c>
+      <c r="U3" s="10">
+        <v>0</v>
+      </c>
+      <c r="V3" s="10">
+        <v>0</v>
+      </c>
+      <c r="W3" s="10">
+        <v>0</v>
+      </c>
+      <c r="X3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>15</v>
+      <c r="A4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>4</v>
@@ -3197,11 +2914,11 @@
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>16</v>
+      <c r="A5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>4</v>
@@ -3331,282 +3048,282 @@
       </c>
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>9</v>
+      <c r="A6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
-        <v>0</v>
-      </c>
-      <c r="S6" s="10">
-        <v>0</v>
-      </c>
-      <c r="T6" s="10">
-        <v>0</v>
-      </c>
-      <c r="U6" s="10">
-        <v>0</v>
-      </c>
-      <c r="V6" s="10">
-        <v>0</v>
-      </c>
-      <c r="W6" s="10">
-        <v>0</v>
-      </c>
-      <c r="X6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="10">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR6" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>8</v>
+      <c r="B7" s="19" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR7" s="19" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>10</v>
-      </c>
       <c r="C8" s="11" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
@@ -3733,145 +3450,145 @@
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>7</v>
+      <c r="A9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ9" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR9" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0</v>
+      </c>
+      <c r="P9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>0</v>
+      </c>
+      <c r="R9" s="10">
+        <v>0</v>
+      </c>
+      <c r="S9" s="10">
+        <v>0</v>
+      </c>
+      <c r="T9" s="10">
+        <v>0</v>
+      </c>
+      <c r="U9" s="10">
+        <v>0</v>
+      </c>
+      <c r="V9" s="10">
+        <v>0</v>
+      </c>
+      <c r="W9" s="10">
+        <v>0</v>
+      </c>
+      <c r="X9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>15</v>
+      <c r="A10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>4</v>
@@ -4001,404 +3718,136 @@
       </c>
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>13</v>
+      <c r="A11" s="14" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10">
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
-        <v>0</v>
-      </c>
-      <c r="N11" s="10">
-        <v>0</v>
-      </c>
-      <c r="O11" s="10">
-        <v>0</v>
-      </c>
-      <c r="P11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>0</v>
-      </c>
-      <c r="R11" s="10">
-        <v>0</v>
-      </c>
-      <c r="S11" s="10">
-        <v>0</v>
-      </c>
-      <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10">
-        <v>0</v>
-      </c>
-      <c r="V11" s="10">
-        <v>0</v>
-      </c>
-      <c r="W11" s="10">
-        <v>0</v>
-      </c>
-      <c r="X11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0</v>
-      </c>
-      <c r="J12" s="10">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0</v>
-      </c>
-      <c r="M12" s="10">
-        <v>0</v>
-      </c>
-      <c r="N12" s="10">
-        <v>0</v>
-      </c>
-      <c r="O12" s="10">
-        <v>0</v>
-      </c>
-      <c r="P12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>0</v>
-      </c>
-      <c r="R12" s="10">
-        <v>0</v>
-      </c>
-      <c r="S12" s="10">
-        <v>0</v>
-      </c>
-      <c r="T12" s="10">
-        <v>0</v>
-      </c>
-      <c r="U12" s="10">
-        <v>0</v>
-      </c>
-      <c r="V12" s="10">
-        <v>0</v>
-      </c>
-      <c r="W12" s="10">
-        <v>0</v>
-      </c>
-      <c r="X12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="19">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AR13" s="19" t="s">
+      <c r="D11" s="17">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="R11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="V11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="W11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="X11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR11" s="17" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4409,7 +3858,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05BBA240-3A33-412F-B1CD-E7904F3C1D3D}">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -4419,7 +3868,7 @@
       <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6">
@@ -4547,11 +3996,11 @@
       </c>
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="C2" s="10">
         <v>0</v>
@@ -4678,139 +4127,139 @@
       </c>
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
-        <v>7</v>
+      <c r="A3" s="14" t="s">
+        <v>13</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="S3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="T3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="V3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="W3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="X3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ3" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0</v>
+      </c>
+      <c r="O3" s="10">
+        <v>0</v>
+      </c>
+      <c r="P3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10">
+        <v>0</v>
+      </c>
+      <c r="R3" s="10">
+        <v>0</v>
+      </c>
+      <c r="S3" s="10">
+        <v>0</v>
+      </c>
+      <c r="T3" s="10">
+        <v>0</v>
+      </c>
+      <c r="U3" s="10">
+        <v>0</v>
+      </c>
+      <c r="V3" s="10">
+        <v>0</v>
+      </c>
+      <c r="W3" s="10">
+        <v>0</v>
+      </c>
+      <c r="X3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>15</v>
+      <c r="A4" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>4</v>
@@ -4940,8 +4389,8 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>16</v>
+      <c r="A5" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>4</v>
@@ -5071,264 +4520,133 @@
       </c>
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>9</v>
+      <c r="A6" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="10">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <v>0</v>
-      </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10">
-        <v>0</v>
-      </c>
-      <c r="O6" s="10">
-        <v>0</v>
-      </c>
-      <c r="P6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>0</v>
-      </c>
-      <c r="R6" s="10">
-        <v>0</v>
-      </c>
-      <c r="S6" s="10">
-        <v>0</v>
-      </c>
-      <c r="T6" s="10">
-        <v>0</v>
-      </c>
-      <c r="U6" s="10">
-        <v>0</v>
-      </c>
-      <c r="V6" s="10">
-        <v>0</v>
-      </c>
-      <c r="W6" s="10">
-        <v>0</v>
-      </c>
-      <c r="X6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="19">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="N7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="R7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="S7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="T7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="U7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="W7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="X7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Y7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AL7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AM7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AN7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AO7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AP7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="AQ7" s="19" t="s">
+      <c r="C6" s="17">
+        <v>0</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="X6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AO6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="AQ6" s="17" t="s">
         <v>6</v>
       </c>
     </row>
